--- a/Result/profitability/4153.xlsx
+++ b/Result/profitability/4153.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM63"/>
+  <dimension ref="A1:AM64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.24</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3575</v>
+        <v>0.39125</v>
       </c>
       <c r="N2" t="n">
-        <v>28.355</v>
+        <v>28.17125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>1.09</v>
       </c>
       <c r="M3" t="n">
-        <v>0.46125</v>
+        <v>0.4775</v>
       </c>
       <c r="N3" t="n">
-        <v>27.04625</v>
+        <v>26.98125</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -8435,6 +8435,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>4153</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>245</v>
+      </c>
+      <c r="D64" t="n">
+        <v>173</v>
+      </c>
+      <c r="E64" t="n">
+        <v>72</v>
+      </c>
+      <c r="F64" t="n">
+        <v>29.29</v>
+      </c>
+      <c r="G64" t="n">
+        <v>31</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>12.83%</t>
+        </is>
+      </c>
+      <c r="I64" t="n">
+        <v>1</v>
+      </c>
+      <c r="J64" t="n">
+        <v>33</v>
+      </c>
+      <c r="K64" t="n">
+        <v>31</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0.39375</v>
+      </c>
+      <c r="N64" t="n">
+        <v>29.8675</v>
+      </c>
+      <c r="O64" t="n">
+        <v>1</v>
+      </c>
+      <c r="P64" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>1</v>
+      </c>
+      <c r="R64" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" t="n">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>0</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
+      </c>
+      <c r="V64" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W64" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="X64" t="n">
+        <v>0.2619047619047621</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>1.449999999999999</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>0.05208333333333326</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>0.09000000000000002</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>0.2045454545454546</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>-1.260000000000002</v>
+      </c>
+      <c r="AD64" t="n">
+        <v>-0.04124386252045831</v>
+      </c>
+      <c r="AE64" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF64" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG64" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK64" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL64" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM64" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
